--- a/Copy of Wholesale prices - 2007-2022.xlsx
+++ b/Copy of Wholesale prices - 2007-2022.xlsx
@@ -264,16 +264,16 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -12056,7 +12056,7 @@
         <v>14</v>
       </c>
       <c r="B263" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C263" s="5">
         <v>9.204273504273507</v>
@@ -12100,7 +12100,7 @@
         <v>15</v>
       </c>
       <c r="B264" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C264" s="5">
         <v>5.377777777777778</v>
@@ -12144,7 +12144,7 @@
         <v>16</v>
       </c>
       <c r="B265" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C265" s="5">
         <v>4.503418803418803</v>
@@ -12188,7 +12188,7 @@
         <v>17</v>
       </c>
       <c r="B266" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C266" s="5">
         <v>6.364957264957266</v>
@@ -12232,7 +12232,7 @@
         <v>18</v>
       </c>
       <c r="B267" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C267" s="5">
         <v>7.307008547008547</v>
@@ -12276,7 +12276,7 @@
         <v>19</v>
       </c>
       <c r="B268" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C268" s="5">
         <v>5.979487179487181</v>
@@ -12320,7 +12320,7 @@
         <v>20</v>
       </c>
       <c r="B269" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C269" s="5">
         <v>2.938034188034189</v>
@@ -12364,7 +12364,7 @@
         <v>21</v>
       </c>
       <c r="B270" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C270" s="5">
         <v>3.384615384615385</v>
@@ -12408,7 +12408,7 @@
         <v>45</v>
       </c>
       <c r="B271" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C271" s="5">
         <v>1.7085470085470083</v>
@@ -12452,7 +12452,7 @@
         <v>22</v>
       </c>
       <c r="B272" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C272" s="5">
         <v>2.2</v>
@@ -12496,7 +12496,7 @@
         <v>23</v>
       </c>
       <c r="B273" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C273" s="5">
         <v>3.944017094017094</v>
@@ -12540,7 +12540,7 @@
         <v>24</v>
       </c>
       <c r="B274" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C274" s="5">
         <v>7.568376068376069</v>
@@ -12584,7 +12584,7 @@
         <v>25</v>
       </c>
       <c r="B275" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C275" s="5">
         <v>1.9837606837606843</v>
@@ -12628,7 +12628,7 @@
         <v>26</v>
       </c>
       <c r="B276" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C276" s="5">
         <v>2.108803418803419</v>
@@ -12672,7 +12672,7 @@
         <v>27</v>
       </c>
       <c r="B277" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C277" s="5">
         <v>3.0461538461538464</v>
@@ -12716,7 +12716,7 @@
         <v>28</v>
       </c>
       <c r="B278" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C278" s="5">
         <v>9.722364672364671</v>
@@ -12760,7 +12760,7 @@
         <v>46</v>
       </c>
       <c r="B279" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C279" s="5">
         <v>7.055982905982906</v>
@@ -12804,7 +12804,7 @@
         <v>30</v>
       </c>
       <c r="B280" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C280" s="5">
         <v>1.9894017094017094</v>
@@ -12848,7 +12848,7 @@
         <v>31</v>
       </c>
       <c r="B281" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C281" s="5">
         <v>3.9863247863247873</v>
@@ -12892,7 +12892,7 @@
         <v>32</v>
       </c>
       <c r="B282" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C282" s="5">
         <v>6.285982905982906</v>
@@ -12936,7 +12936,7 @@
         <v>33</v>
       </c>
       <c r="B283" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C283" s="5">
         <v>3.6405299145299144</v>
@@ -12980,7 +12980,7 @@
         <v>34</v>
       </c>
       <c r="B284" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C284" s="5">
         <v>3.3705128205128205</v>
@@ -13024,7 +13024,7 @@
         <v>35</v>
       </c>
       <c r="B285" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C285" s="5">
         <v>6.8341025641025634</v>
@@ -13068,7 +13068,7 @@
         <v>36</v>
       </c>
       <c r="B286" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C286" s="5">
         <v>11.0</v>
@@ -13112,7 +13112,7 @@
         <v>42</v>
       </c>
       <c r="B287" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C287" s="5">
         <v>4.447008547008547</v>
@@ -13156,7 +13156,7 @@
         <v>37</v>
       </c>
       <c r="B288" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C288" s="5">
         <v>33.0</v>
@@ -13200,7 +13200,7 @@
         <v>38</v>
       </c>
       <c r="B289" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C289" s="5">
         <v>22.0</v>
@@ -13244,7 +13244,7 @@
         <v>39</v>
       </c>
       <c r="B290" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C290" s="5">
         <v>5.081623931623932</v>
@@ -13288,7 +13288,7 @@
         <v>40</v>
       </c>
       <c r="B291" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C291" s="5">
         <v>38.48253968253968</v>
@@ -13332,7 +13332,7 @@
         <v>47</v>
       </c>
       <c r="B292" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C292" s="5">
         <v>2.9596581196581195</v>
@@ -13376,7 +13376,7 @@
         <v>41</v>
       </c>
       <c r="B293" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C293" s="5">
         <v>4.161666666666667</v>
@@ -13420,7 +13420,7 @@
         <v>43</v>
       </c>
       <c r="B294" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C294" s="5">
         <v>4.803333333333334</v>
@@ -13464,7 +13464,7 @@
         <v>44</v>
       </c>
       <c r="B295" s="11">
-        <v>42006.0</v>
+        <v>2015.0</v>
       </c>
       <c r="C295" s="5">
         <v>3.901709401709402</v>
@@ -13508,7 +13508,7 @@
         <v>14</v>
       </c>
       <c r="B296" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C296" s="5">
         <v>8.733247863247863</v>
@@ -13552,7 +13552,7 @@
         <v>15</v>
       </c>
       <c r="B297" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C297" s="5">
         <v>5.735042735042736</v>
@@ -13596,7 +13596,7 @@
         <v>16</v>
       </c>
       <c r="B298" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C298" s="5">
         <v>4.823076923076925</v>
@@ -13640,7 +13640,7 @@
         <v>17</v>
       </c>
       <c r="B299" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C299" s="5">
         <v>6.017094017094017</v>
@@ -13684,7 +13684,7 @@
         <v>18</v>
       </c>
       <c r="B300" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C300" s="5">
         <v>7.051282051282052</v>
@@ -13728,7 +13728,7 @@
         <v>19</v>
       </c>
       <c r="B301" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C301" s="5">
         <v>7.347435897435897</v>
@@ -13772,7 +13772,7 @@
         <v>20</v>
       </c>
       <c r="B302" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C302" s="5">
         <v>3.1834188034188036</v>
@@ -13816,7 +13816,7 @@
         <v>21</v>
       </c>
       <c r="B303" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C303" s="5">
         <v>2.858119658119659</v>
@@ -13860,7 +13860,7 @@
         <v>45</v>
       </c>
       <c r="B304" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C304" s="5">
         <v>1.4790598290598291</v>
@@ -13904,7 +13904,7 @@
         <v>22</v>
       </c>
       <c r="B305" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C305" s="5">
         <v>2.2</v>
@@ -13948,7 +13948,7 @@
         <v>23</v>
       </c>
       <c r="B306" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C306" s="5">
         <v>3.995726495726496</v>
@@ -13992,7 +13992,7 @@
         <v>24</v>
       </c>
       <c r="B307" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C307" s="5">
         <v>6.604700854700855</v>
@@ -14036,7 +14036,7 @@
         <v>25</v>
       </c>
       <c r="B308" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C308" s="5">
         <v>2.4660683760683764</v>
@@ -14080,7 +14080,7 @@
         <v>26</v>
       </c>
       <c r="B309" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C309" s="5">
         <v>2.851538461538462</v>
@@ -14124,7 +14124,7 @@
         <v>27</v>
       </c>
       <c r="B310" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C310" s="5">
         <v>3.196424501424502</v>
@@ -14168,7 +14168,7 @@
         <v>28</v>
       </c>
       <c r="B311" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C311" s="5">
         <v>9.354700854700855</v>
@@ -14212,7 +14212,7 @@
         <v>46</v>
       </c>
       <c r="B312" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C312" s="5">
         <v>5.185042735042735</v>
@@ -14256,7 +14256,7 @@
         <v>30</v>
       </c>
       <c r="B313" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C313" s="5">
         <v>1.9884615384615387</v>
@@ -14300,7 +14300,7 @@
         <v>31</v>
       </c>
       <c r="B314" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C314" s="5">
         <v>3.9064102564102567</v>
@@ -14344,7 +14344,7 @@
         <v>32</v>
       </c>
       <c r="B315" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C315" s="5">
         <v>6.750427350427351</v>
@@ -14388,7 +14388,7 @@
         <v>33</v>
       </c>
       <c r="B316" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C316" s="5">
         <v>3.6928034188034187</v>
@@ -14432,7 +14432,7 @@
         <v>34</v>
       </c>
       <c r="B317" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C317" s="5">
         <v>5.26965811965812</v>
@@ -14476,7 +14476,7 @@
         <v>35</v>
       </c>
       <c r="B318" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C318" s="5">
         <v>7.386923076923078</v>
@@ -14520,7 +14520,7 @@
         <v>36</v>
       </c>
       <c r="B319" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C319" s="5">
         <v>11.0</v>
@@ -14564,7 +14564,7 @@
         <v>42</v>
       </c>
       <c r="B320" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C320" s="5">
         <v>5.5</v>
@@ -14608,7 +14608,7 @@
         <v>37</v>
       </c>
       <c r="B321" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C321" s="5">
         <v>35.475</v>
@@ -14652,7 +14652,7 @@
         <v>38</v>
       </c>
       <c r="B322" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C322" s="5">
         <v>21.908333333333335</v>
@@ -14696,7 +14696,7 @@
         <v>39</v>
       </c>
       <c r="B323" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C323" s="5">
         <v>5.175641025641027</v>
@@ -14740,7 +14740,7 @@
         <v>40</v>
       </c>
       <c r="B324" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C324" s="5">
         <v>40.7</v>
@@ -14784,7 +14784,7 @@
         <v>47</v>
       </c>
       <c r="B325" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C325" s="5">
         <v>3.005350427350427</v>
@@ -14828,7 +14828,7 @@
         <v>41</v>
       </c>
       <c r="B326" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C326" s="5">
         <v>4.103846153846154</v>
@@ -14872,7 +14872,7 @@
         <v>43</v>
       </c>
       <c r="B327" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C327" s="5">
         <v>4.893589743589744</v>
@@ -14916,7 +14916,7 @@
         <v>44</v>
       </c>
       <c r="B328" s="11">
-        <v>42370.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C328" s="5">
         <v>4.00982905982906</v>
@@ -14960,7 +14960,7 @@
         <v>14</v>
       </c>
       <c r="B329" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C329" s="5">
         <v>11.145726495726498</v>
@@ -15004,7 +15004,7 @@
         <v>15</v>
       </c>
       <c r="B330" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C330" s="5">
         <v>5.203846153846154</v>
@@ -15048,7 +15048,7 @@
         <v>16</v>
       </c>
       <c r="B331" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C331" s="5">
         <v>5.099487179487181</v>
@@ -15092,7 +15092,7 @@
         <v>17</v>
       </c>
       <c r="B332" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C332" s="5">
         <v>6.698717948717949</v>
@@ -15136,7 +15136,7 @@
         <v>18</v>
       </c>
       <c r="B333" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C333" s="5">
         <v>7.192307692307693</v>
@@ -15180,7 +15180,7 @@
         <v>19</v>
       </c>
       <c r="B334" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C334" s="5">
         <v>7.5420512820512835</v>
@@ -15224,7 +15224,7 @@
         <v>20</v>
       </c>
       <c r="B335" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C335" s="5">
         <v>3.194512820512821</v>
@@ -15268,7 +15268,7 @@
         <v>21</v>
       </c>
       <c r="B336" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C336" s="5">
         <v>2.9756410256410266</v>
@@ -15312,7 +15312,7 @@
         <v>45</v>
       </c>
       <c r="B337" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C337" s="5">
         <v>2.6512820512820525</v>
@@ -15356,7 +15356,7 @@
         <v>22</v>
       </c>
       <c r="B338" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C338" s="5">
         <v>2.175555555555556</v>
@@ -15400,7 +15400,7 @@
         <v>23</v>
       </c>
       <c r="B339" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C339" s="5">
         <v>4.964102564102564</v>
@@ -15444,7 +15444,7 @@
         <v>24</v>
       </c>
       <c r="B340" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C340" s="5">
         <v>8.212393162393163</v>
@@ -15488,7 +15488,7 @@
         <v>25</v>
       </c>
       <c r="B341" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C341" s="5">
         <v>2.0900000000000003</v>
@@ -15532,7 +15532,7 @@
         <v>26</v>
       </c>
       <c r="B342" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C342" s="5">
         <v>2.693589743589743</v>
@@ -15576,7 +15576,7 @@
         <v>27</v>
       </c>
       <c r="B343" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C343" s="5">
         <v>4.174358974358975</v>
@@ -15620,7 +15620,7 @@
         <v>28</v>
       </c>
       <c r="B344" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C344" s="5">
         <v>9.9</v>
@@ -15664,7 +15664,7 @@
         <v>46</v>
       </c>
       <c r="B345" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C345" s="5">
         <v>7.784615384615385</v>
@@ -15708,7 +15708,7 @@
         <v>30</v>
       </c>
       <c r="B346" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C346" s="5">
         <v>1.9931623931623936</v>
@@ -15752,7 +15752,7 @@
         <v>31</v>
       </c>
       <c r="B347" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C347" s="5">
         <v>4.16965811965812</v>
@@ -15796,7 +15796,7 @@
         <v>32</v>
       </c>
       <c r="B348" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C348" s="5">
         <v>6.701538461538463</v>
@@ -15840,7 +15840,7 @@
         <v>33</v>
       </c>
       <c r="B349" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C349" s="5">
         <v>3.8964444444444455</v>
@@ -15884,7 +15884,7 @@
         <v>34</v>
       </c>
       <c r="B350" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C350" s="5">
         <v>4.174358974358975</v>
@@ -15928,7 +15928,7 @@
         <v>35</v>
       </c>
       <c r="B351" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C351" s="5">
         <v>7.4461538461538455</v>
@@ -15972,7 +15972,7 @@
         <v>36</v>
       </c>
       <c r="B352" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C352" s="5">
         <v>11.0</v>
@@ -16016,7 +16016,7 @@
         <v>42</v>
       </c>
       <c r="B353" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C353" s="5">
         <v>5.0346153846153845</v>
@@ -16060,7 +16060,7 @@
         <v>37</v>
       </c>
       <c r="B354" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C354" s="5">
         <v>30.2775</v>
@@ -16104,7 +16104,7 @@
         <v>38</v>
       </c>
       <c r="B355" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C355" s="5">
         <v>24.7775</v>
@@ -16148,7 +16148,7 @@
         <v>39</v>
       </c>
       <c r="B356" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C356" s="5">
         <v>5.288461538461538</v>
@@ -16192,7 +16192,7 @@
         <v>40</v>
       </c>
       <c r="B357" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C357" s="5">
         <v>33.21083333333333</v>
@@ -16236,7 +16236,7 @@
         <v>47</v>
       </c>
       <c r="B358" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C358" s="5">
         <v>3.174769230769231</v>
@@ -16280,7 +16280,7 @@
         <v>49</v>
       </c>
       <c r="B359" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C359" s="5">
         <v>3.9346153846153853</v>
@@ -16324,7 +16324,7 @@
         <v>43</v>
       </c>
       <c r="B360" s="11">
-        <v>42736.0</v>
+        <v>2017.0</v>
       </c>
       <c r="C360" s="5">
         <v>4.823076923076925</v>
@@ -16367,8 +16367,8 @@
       <c r="A361" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B361" s="13">
-        <v>42736.0</v>
+      <c r="B361" s="11">
+        <v>2017.0</v>
       </c>
       <c r="C361" s="7">
         <v>3.9346153846153853</v>
@@ -16412,7 +16412,7 @@
         <v>14</v>
       </c>
       <c r="B362" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C362" s="5">
         <v>8.875213675213676</v>
@@ -16456,7 +16456,7 @@
         <v>15</v>
       </c>
       <c r="B363" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C363" s="5">
         <v>5.584615384615385</v>
@@ -16500,7 +16500,7 @@
         <v>16</v>
       </c>
       <c r="B364" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C364" s="5">
         <v>4.823076923076925</v>
@@ -16544,7 +16544,7 @@
         <v>17</v>
       </c>
       <c r="B365" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C365" s="5">
         <v>6.700128205128205</v>
@@ -16588,7 +16588,7 @@
         <v>18</v>
       </c>
       <c r="B366" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C366" s="5">
         <v>7.276923076923076</v>
@@ -16632,7 +16632,7 @@
         <v>19</v>
       </c>
       <c r="B367" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C367" s="5">
         <v>8.413186813186815</v>
@@ -16676,7 +16676,7 @@
         <v>20</v>
       </c>
       <c r="B368" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C368" s="5">
         <v>2.2646367521367528</v>
@@ -16720,7 +16720,7 @@
         <v>21</v>
       </c>
       <c r="B369" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C369" s="5">
         <v>3.088461538461538</v>
@@ -16764,7 +16764,7 @@
         <v>45</v>
       </c>
       <c r="B370" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C370" s="5">
         <v>2.7129914529914534</v>
@@ -16808,7 +16808,7 @@
         <v>22</v>
       </c>
       <c r="B371" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C371" s="5">
         <v>2.2</v>
@@ -16852,7 +16852,7 @@
         <v>23</v>
       </c>
       <c r="B372" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C372" s="5">
         <v>4.352991452991452</v>
@@ -16896,7 +16896,7 @@
         <v>24</v>
       </c>
       <c r="B373" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C373" s="5">
         <v>7.702350427350428</v>
@@ -16940,7 +16940,7 @@
         <v>25</v>
       </c>
       <c r="B374" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C374" s="5">
         <v>3.088461538461538</v>
@@ -16984,7 +16984,7 @@
         <v>26</v>
       </c>
       <c r="B375" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C375" s="5">
         <v>3.365811965811966</v>
@@ -17028,7 +17028,7 @@
         <v>27</v>
       </c>
       <c r="B376" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C376" s="5">
         <v>3.795299145299146</v>
@@ -17072,7 +17072,7 @@
         <v>28</v>
       </c>
       <c r="B377" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C377" s="5">
         <v>9.9</v>
@@ -17116,7 +17116,7 @@
         <v>46</v>
       </c>
       <c r="B378" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C378" s="5">
         <v>7.201709401709402</v>
@@ -17160,7 +17160,7 @@
         <v>30</v>
       </c>
       <c r="B379" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C379" s="5">
         <v>1.9884615384615387</v>
@@ -17204,7 +17204,7 @@
         <v>31</v>
       </c>
       <c r="B380" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C380" s="5">
         <v>4.696153846153846</v>
@@ -17248,7 +17248,7 @@
         <v>32</v>
       </c>
       <c r="B381" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C381" s="5">
         <v>6.844444444444445</v>
@@ -17292,7 +17292,7 @@
         <v>33</v>
       </c>
       <c r="B382" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C382" s="5">
         <v>3.907538461538462</v>
@@ -17336,7 +17336,7 @@
         <v>34</v>
       </c>
       <c r="B383" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C383" s="5">
         <v>3.905555555555556</v>
@@ -17380,7 +17380,7 @@
         <v>35</v>
       </c>
       <c r="B384" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C384" s="5">
         <v>6.924358974358974</v>
@@ -17424,7 +17424,7 @@
         <v>36</v>
       </c>
       <c r="B385" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C385" s="5">
         <v>11.150427350427352</v>
@@ -17468,7 +17468,7 @@
         <v>42</v>
       </c>
       <c r="B386" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C386" s="5">
         <v>4.817435897435898</v>
@@ -17512,7 +17512,7 @@
         <v>37</v>
       </c>
       <c r="B387" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C387" s="5">
         <v>32.589444444444446</v>
@@ -17556,7 +17556,7 @@
         <v>38</v>
       </c>
       <c r="B388" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C388" s="5">
         <v>25.061666666666667</v>
@@ -17600,7 +17600,7 @@
         <v>39</v>
       </c>
       <c r="B389" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C389" s="5">
         <v>5.297863247863247</v>
@@ -17644,7 +17644,7 @@
         <v>40</v>
       </c>
       <c r="B390" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C390" s="5">
         <v>35.35953703703703</v>
@@ -17688,7 +17688,7 @@
         <v>47</v>
       </c>
       <c r="B391" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C391" s="5">
         <v>3.1155384615384607</v>
@@ -17732,7 +17732,7 @@
         <v>49</v>
       </c>
       <c r="B392" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C392" s="5">
         <v>4.52974358974359</v>
@@ -17776,7 +17776,7 @@
         <v>43</v>
       </c>
       <c r="B393" s="11">
-        <v>43101.0</v>
+        <v>2018.0</v>
       </c>
       <c r="C393" s="5">
         <v>4.865384615384616</v>
@@ -17819,8 +17819,8 @@
       <c r="A394" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B394" s="13">
-        <v>43101.0</v>
+      <c r="B394" s="11">
+        <v>2018.0</v>
       </c>
       <c r="C394" s="7">
         <v>3.445726495726496</v>
@@ -17864,7 +17864,7 @@
         <v>14</v>
       </c>
       <c r="B395" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C395" s="5">
         <v>7.077920227920227</v>
@@ -17908,7 +17908,7 @@
         <v>15</v>
       </c>
       <c r="B396" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C396" s="5">
         <v>6.285042735042736</v>
@@ -17952,7 +17952,7 @@
         <v>16</v>
       </c>
       <c r="B397" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C397" s="5">
         <v>5.443589743589743</v>
@@ -17996,7 +17996,7 @@
         <v>17</v>
       </c>
       <c r="B398" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C398" s="5">
         <v>7.228739316239316</v>
@@ -18040,7 +18040,7 @@
         <v>18</v>
       </c>
       <c r="B399" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C399" s="5">
         <v>7.455555555555555</v>
@@ -18084,7 +18084,7 @@
         <v>19</v>
       </c>
       <c r="B400" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C400" s="5">
         <v>7.375641025641025</v>
@@ -18128,7 +18128,7 @@
         <v>20</v>
       </c>
       <c r="B401" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C401" s="5">
         <v>2.7185826210826214</v>
@@ -18172,7 +18172,7 @@
         <v>21</v>
       </c>
       <c r="B402" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C402" s="5">
         <v>3.0414529914529913</v>
@@ -18216,7 +18216,7 @@
         <v>45</v>
       </c>
       <c r="B403" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C403" s="5">
         <v>3.368632478632479</v>
@@ -18260,7 +18260,7 @@
         <v>22</v>
       </c>
       <c r="B404" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C404" s="5">
         <v>2.2</v>
@@ -18304,7 +18304,7 @@
         <v>23</v>
       </c>
       <c r="B405" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C405" s="5">
         <v>4.878632478632479</v>
@@ -18348,7 +18348,7 @@
         <v>24</v>
       </c>
       <c r="B406" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C406" s="5">
         <v>6.957264957264959</v>
@@ -18392,7 +18392,7 @@
         <v>25</v>
       </c>
       <c r="B407" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C407" s="5">
         <v>2.796068376068376</v>
@@ -18436,7 +18436,7 @@
         <v>26</v>
       </c>
       <c r="B408" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C408" s="5">
         <v>3.13923076923077</v>
@@ -18480,7 +18480,7 @@
         <v>27</v>
       </c>
       <c r="B409" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C409" s="5">
         <v>2.8529914529914526</v>
@@ -18524,7 +18524,7 @@
         <v>28</v>
       </c>
       <c r="B410" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C410" s="5">
         <v>9.871794871794872</v>
@@ -18568,7 +18568,7 @@
         <v>46</v>
       </c>
       <c r="B411" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C411" s="5">
         <v>4.374145299145301</v>
@@ -18612,7 +18612,7 @@
         <v>30</v>
       </c>
       <c r="B412" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C412" s="5">
         <v>2.2090491452991454</v>
@@ -18656,7 +18656,7 @@
         <v>31</v>
       </c>
       <c r="B413" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C413" s="5">
         <v>4.91298076923077</v>
@@ -18700,7 +18700,7 @@
         <v>32</v>
       </c>
       <c r="B414" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C414" s="5">
         <v>6.956794871794871</v>
@@ -18744,7 +18744,7 @@
         <v>33</v>
       </c>
       <c r="B415" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C415" s="5">
         <v>3.912897435897436</v>
@@ -18788,7 +18788,7 @@
         <v>34</v>
       </c>
       <c r="B416" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C416" s="5">
         <v>5.095726495726496</v>
@@ -18832,7 +18832,7 @@
         <v>35</v>
       </c>
       <c r="B417" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C417" s="5">
         <v>7.422649572649574</v>
@@ -18876,7 +18876,7 @@
         <v>36</v>
       </c>
       <c r="B418" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C418" s="5">
         <v>11.056410256410258</v>
@@ -18920,7 +18920,7 @@
         <v>42</v>
       </c>
       <c r="B419" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C419" s="5">
         <v>4.975384615384614</v>
@@ -18964,7 +18964,7 @@
         <v>37</v>
       </c>
       <c r="B420" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C420" s="5">
         <v>31.141071428571426</v>
@@ -19008,7 +19008,7 @@
         <v>38</v>
       </c>
       <c r="B421" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C421" s="5">
         <v>28.081333333333333</v>
@@ -19052,7 +19052,7 @@
         <v>39</v>
       </c>
       <c r="B422" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C422" s="5">
         <v>5.2547720797720805</v>
@@ -19096,7 +19096,7 @@
         <v>40</v>
       </c>
       <c r="B423" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C423" s="5">
         <v>39.55761111111111</v>
@@ -19140,7 +19140,7 @@
         <v>47</v>
       </c>
       <c r="B424" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C424" s="5">
         <v>2.9150470085470084</v>
@@ -19184,7 +19184,7 @@
         <v>49</v>
       </c>
       <c r="B425" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C425" s="5">
         <v>4.7441025641025645</v>
@@ -19228,7 +19228,7 @@
         <v>43</v>
       </c>
       <c r="B426" s="11">
-        <v>43466.0</v>
+        <v>2019.0</v>
       </c>
       <c r="C426" s="5">
         <v>4.966923076923077</v>
@@ -19271,8 +19271,8 @@
       <c r="A427" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B427" s="13">
-        <v>43466.0</v>
+      <c r="B427" s="11">
+        <v>2019.0</v>
       </c>
       <c r="C427" s="7">
         <v>3.535826210826212</v>
@@ -20723,7 +20723,7 @@
       <c r="A460" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B460" s="14">
+      <c r="B460" s="13">
         <v>2020.0</v>
       </c>
       <c r="C460" s="7">
@@ -20768,7 +20768,7 @@
         <v>14</v>
       </c>
       <c r="B461" s="11">
-        <v>44197.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C461" s="5">
         <v>10.645555555555553</v>
@@ -20812,7 +20812,7 @@
         <v>15</v>
       </c>
       <c r="B462" s="11">
-        <v>44198.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C462" s="5">
         <v>5.706837606837608</v>
@@ -20856,7 +20856,7 @@
         <v>16</v>
       </c>
       <c r="B463" s="11">
-        <v>44199.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C463" s="5">
         <v>4.893589743589743</v>
@@ -20900,7 +20900,7 @@
         <v>17</v>
       </c>
       <c r="B464" s="11">
-        <v>44200.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C464" s="5">
         <v>6.783333333333335</v>
@@ -20944,7 +20944,7 @@
         <v>18</v>
       </c>
       <c r="B465" s="11">
-        <v>44201.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C465" s="5">
         <v>7.24777777777778</v>
@@ -20988,7 +20988,7 @@
         <v>19</v>
       </c>
       <c r="B466" s="11">
-        <v>44202.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C466" s="5">
         <v>7.883333333333335</v>
@@ -21032,7 +21032,7 @@
         <v>20</v>
       </c>
       <c r="B467" s="11">
-        <v>44203.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C467" s="5">
         <v>3.065897435897436</v>
@@ -21076,7 +21076,7 @@
         <v>21</v>
       </c>
       <c r="B468" s="11">
-        <v>44204.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C468" s="5">
         <v>3.3000000000000003</v>
@@ -21120,7 +21120,7 @@
         <v>45</v>
       </c>
       <c r="B469" s="11">
-        <v>44205.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C469" s="5">
         <v>5.445</v>
@@ -21164,7 +21164,7 @@
         <v>22</v>
       </c>
       <c r="B470" s="11">
-        <v>44206.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C470" s="5">
         <v>2.5300000000000007</v>
@@ -21208,7 +21208,7 @@
         <v>23</v>
       </c>
       <c r="B471" s="11">
-        <v>44207.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C471" s="5">
         <v>4.6209401709401705</v>
@@ -21252,7 +21252,7 @@
         <v>24</v>
       </c>
       <c r="B472" s="11">
-        <v>44208.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C472" s="5">
         <v>8.54351851851852</v>
@@ -21296,7 +21296,7 @@
         <v>25</v>
       </c>
       <c r="B473" s="11">
-        <v>44209.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C473" s="5">
         <v>2.1185185185185187</v>
@@ -21340,7 +21340,7 @@
         <v>26</v>
       </c>
       <c r="B474" s="11">
-        <v>44210.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C474" s="5">
         <v>3.2083333333333335</v>
@@ -21384,7 +21384,7 @@
         <v>27</v>
       </c>
       <c r="B475" s="11">
-        <v>44211.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C475" s="5">
         <v>4.7555555555555555</v>
@@ -21428,7 +21428,7 @@
         <v>28</v>
       </c>
       <c r="B476" s="11">
-        <v>44212.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C476" s="5">
         <v>9.6</v>
@@ -21472,7 +21472,7 @@
         <v>46</v>
       </c>
       <c r="B477" s="11">
-        <v>44213.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C477" s="5">
         <v>7.883333333333335</v>
@@ -21516,7 +21516,7 @@
         <v>30</v>
       </c>
       <c r="B478" s="11">
-        <v>44215.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C478" s="5">
         <v>1.8333333333333333</v>
@@ -21560,7 +21560,7 @@
         <v>31</v>
       </c>
       <c r="B479" s="11">
-        <v>44216.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C479" s="5">
         <v>4.904166666666667</v>
@@ -21604,7 +21604,7 @@
         <v>32</v>
       </c>
       <c r="B480" s="11">
-        <v>44217.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C480" s="5">
         <v>7.608333333333333</v>
@@ -21648,7 +21648,7 @@
         <v>33</v>
       </c>
       <c r="B481" s="11">
-        <v>44218.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C481" s="5">
         <v>4.015</v>
@@ -21692,7 +21692,7 @@
         <v>34</v>
       </c>
       <c r="B482" s="11">
-        <v>44219.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C482" s="5">
         <v>5.143518518518518</v>
@@ -21736,7 +21736,7 @@
         <v>35</v>
       </c>
       <c r="B483" s="11">
-        <v>44220.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C483" s="5">
         <v>7.638888888888888</v>
@@ -21780,7 +21780,7 @@
         <v>36</v>
       </c>
       <c r="B484" s="11">
-        <v>44222.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C484" s="5">
         <v>11.0</v>
@@ -21824,7 +21824,7 @@
         <v>42</v>
       </c>
       <c r="B485" s="11">
-        <v>44223.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C485" s="5">
         <v>5.184259259259259</v>
@@ -21868,7 +21868,7 @@
         <v>37</v>
       </c>
       <c r="B486" s="11">
-        <v>44224.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C486" s="5">
         <v>34.76</v>
@@ -21912,7 +21912,7 @@
         <v>38</v>
       </c>
       <c r="B487" s="11">
-        <v>44225.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C487" s="5">
         <v>29.26</v>
@@ -21956,7 +21956,7 @@
         <v>39</v>
       </c>
       <c r="B488" s="11">
-        <v>44226.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C488" s="5">
         <v>5.38287037037037</v>
@@ -22000,7 +22000,7 @@
         <v>40</v>
       </c>
       <c r="B489" s="11">
-        <v>44227.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C489" s="5">
         <v>36.080000000000005</v>
@@ -22044,7 +22044,7 @@
         <v>47</v>
       </c>
       <c r="B490" s="11">
-        <v>44229.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C490" s="5">
         <v>3.08</v>
@@ -22088,7 +22088,7 @@
         <v>49</v>
       </c>
       <c r="B491" s="11">
-        <v>44230.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C491" s="5">
         <v>3.642222222222222</v>
@@ -22132,7 +22132,7 @@
         <v>43</v>
       </c>
       <c r="B492" s="11">
-        <v>44231.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C492" s="5">
         <v>5.194444444444445</v>
@@ -22175,8 +22175,8 @@
       <c r="A493" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B493" s="13">
-        <v>44232.0</v>
+      <c r="B493" s="11">
+        <v>2021.0</v>
       </c>
       <c r="C493" s="7">
         <v>3.817203703703704</v>
@@ -22220,7 +22220,7 @@
         <v>14</v>
       </c>
       <c r="B494" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C494" s="5">
         <v>10.864285714285712</v>
@@ -22264,7 +22264,7 @@
         <v>15</v>
       </c>
       <c r="B495" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C495" s="5">
         <v>6.187500000000001</v>
@@ -22308,7 +22308,7 @@
         <v>16</v>
       </c>
       <c r="B496" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C496" s="5">
         <v>4.766666666666667</v>
@@ -22352,7 +22352,7 @@
         <v>17</v>
       </c>
       <c r="B497" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C497" s="5">
         <v>6.875000000000001</v>
@@ -22396,7 +22396,7 @@
         <v>18</v>
       </c>
       <c r="B498" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C498" s="5">
         <v>7.700000000000001</v>
@@ -22440,7 +22440,7 @@
         <v>19</v>
       </c>
       <c r="B499" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C499" s="5">
         <v>8.197619047619048</v>
@@ -22484,7 +22484,7 @@
         <v>20</v>
       </c>
       <c r="B500" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C500" s="5">
         <v>3.3654761904761905</v>
@@ -22528,7 +22528,7 @@
         <v>21</v>
       </c>
       <c r="B501" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C501" s="5">
         <v>3.208333333333334</v>
@@ -22572,7 +22572,7 @@
         <v>45</v>
       </c>
       <c r="B502" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C502" s="5">
         <v>2.475</v>
@@ -22616,7 +22616,7 @@
         <v>22</v>
       </c>
       <c r="B503" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C503" s="5">
         <v>2.5300000000000007</v>
@@ -22660,7 +22660,7 @@
         <v>23</v>
       </c>
       <c r="B504" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C504" s="5">
         <v>4.7666666666666675</v>
@@ -22704,7 +22704,7 @@
         <v>24</v>
       </c>
       <c r="B505" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C505" s="5">
         <v>8.086309523809524</v>
@@ -22748,7 +22748,7 @@
         <v>25</v>
       </c>
       <c r="B506" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C506" s="5">
         <v>2.370238095238095</v>
@@ -22792,7 +22792,7 @@
         <v>26</v>
       </c>
       <c r="B507" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C507" s="5">
         <v>3.142857142857143</v>
@@ -22836,7 +22836,7 @@
         <v>27</v>
       </c>
       <c r="B508" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C508" s="5">
         <v>2.736904761904762</v>
@@ -22880,7 +22880,7 @@
         <v>28</v>
       </c>
       <c r="B509" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C509" s="5">
         <v>9.9</v>
@@ -22924,7 +22924,7 @@
         <v>46</v>
       </c>
       <c r="B510" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C510" s="5">
         <v>3.6404761904761904</v>
@@ -22968,7 +22968,7 @@
         <v>30</v>
       </c>
       <c r="B511" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C511" s="5">
         <v>1.8400000000000005</v>
@@ -23012,7 +23012,7 @@
         <v>31</v>
       </c>
       <c r="B512" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C512" s="5">
         <v>4.904166666666667</v>
@@ -23056,7 +23056,7 @@
         <v>32</v>
       </c>
       <c r="B513" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C513" s="5">
         <v>7.608333333333333</v>
@@ -23100,7 +23100,7 @@
         <v>33</v>
       </c>
       <c r="B514" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C514" s="5">
         <v>4.302571428571429</v>
@@ -23144,7 +23144,7 @@
         <v>34</v>
       </c>
       <c r="B515" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C515" s="5">
         <v>3.980952380952382</v>
@@ -23188,7 +23188,7 @@
         <v>35</v>
       </c>
       <c r="B516" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C516" s="5">
         <v>7.883333333333334</v>
@@ -23232,7 +23232,7 @@
         <v>36</v>
       </c>
       <c r="B517" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C517" s="5">
         <v>11.916666666666666</v>
@@ -23276,7 +23276,7 @@
         <v>42</v>
       </c>
       <c r="B518" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C518" s="5">
         <v>5.29047619047619</v>
@@ -23320,7 +23320,7 @@
         <v>37</v>
       </c>
       <c r="B519" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C519" s="5">
         <v>45.4404761904762</v>
@@ -23364,7 +23364,7 @@
         <v>38</v>
       </c>
       <c r="B520" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C520" s="5">
         <v>43.50238095238095</v>
@@ -23408,7 +23408,7 @@
         <v>39</v>
       </c>
       <c r="B521" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C521" s="5">
         <v>5.820833333333334</v>
@@ -23452,7 +23452,7 @@
         <v>40</v>
       </c>
       <c r="B522" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C522" s="5">
         <v>52.800000000000004</v>
@@ -23496,7 +23496,7 @@
         <v>47</v>
       </c>
       <c r="B523" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C523" s="5">
         <v>3.056428571428571</v>
@@ -23540,7 +23540,7 @@
         <v>41</v>
       </c>
       <c r="B524" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C524" s="5">
         <v>4.192222222222222</v>
@@ -23584,7 +23584,7 @@
         <v>43</v>
       </c>
       <c r="B525" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C525" s="5">
         <v>5.2555555555555555</v>
@@ -23628,7 +23628,7 @@
         <v>44</v>
       </c>
       <c r="B526" s="11">
-        <v>44568.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C526" s="5">
         <v>3.5291666666666672</v>
@@ -23669,7 +23669,7 @@
     </row>
     <row r="527">
       <c r="A527" s="3"/>
-      <c r="B527" s="11"/>
+      <c r="B527" s="14"/>
       <c r="C527" s="5"/>
       <c r="D527" s="5"/>
       <c r="E527" s="5"/>
@@ -23685,7 +23685,7 @@
     </row>
     <row r="528">
       <c r="A528" s="3"/>
-      <c r="B528" s="11"/>
+      <c r="B528" s="14"/>
       <c r="C528" s="5"/>
       <c r="D528" s="5"/>
       <c r="E528" s="5"/>
@@ -23701,7 +23701,7 @@
     </row>
     <row r="529">
       <c r="A529" s="3"/>
-      <c r="B529" s="11"/>
+      <c r="B529" s="14"/>
       <c r="C529" s="5"/>
       <c r="D529" s="5"/>
       <c r="E529" s="5"/>
@@ -23717,7 +23717,7 @@
     </row>
     <row r="530">
       <c r="A530" s="3"/>
-      <c r="B530" s="11"/>
+      <c r="B530" s="14"/>
       <c r="C530" s="5"/>
       <c r="D530" s="5"/>
       <c r="E530" s="5"/>
@@ -23733,7 +23733,7 @@
     </row>
     <row r="531">
       <c r="A531" s="3"/>
-      <c r="B531" s="11"/>
+      <c r="B531" s="14"/>
       <c r="C531" s="5"/>
       <c r="D531" s="5"/>
       <c r="E531" s="5"/>
@@ -23749,7 +23749,7 @@
     </row>
     <row r="532">
       <c r="A532" s="3"/>
-      <c r="B532" s="11"/>
+      <c r="B532" s="14"/>
       <c r="C532" s="5"/>
       <c r="D532" s="5"/>
       <c r="E532" s="5"/>
@@ -23765,7 +23765,7 @@
     </row>
     <row r="533">
       <c r="A533" s="3"/>
-      <c r="B533" s="11"/>
+      <c r="B533" s="14"/>
       <c r="C533" s="5"/>
       <c r="D533" s="5"/>
       <c r="E533" s="5"/>
@@ -23781,7 +23781,7 @@
     </row>
     <row r="534">
       <c r="A534" s="3"/>
-      <c r="B534" s="11"/>
+      <c r="B534" s="14"/>
       <c r="C534" s="5"/>
       <c r="D534" s="5"/>
       <c r="E534" s="5"/>
@@ -23797,7 +23797,7 @@
     </row>
     <row r="535">
       <c r="A535" s="3"/>
-      <c r="B535" s="11"/>
+      <c r="B535" s="14"/>
       <c r="C535" s="5"/>
       <c r="D535" s="5"/>
       <c r="E535" s="5"/>
@@ -23813,7 +23813,7 @@
     </row>
     <row r="536">
       <c r="A536" s="3"/>
-      <c r="B536" s="11"/>
+      <c r="B536" s="14"/>
       <c r="C536" s="5"/>
       <c r="D536" s="5"/>
       <c r="E536" s="5"/>
@@ -23829,7 +23829,7 @@
     </row>
     <row r="537">
       <c r="A537" s="3"/>
-      <c r="B537" s="11"/>
+      <c r="B537" s="14"/>
       <c r="C537" s="5"/>
       <c r="D537" s="5"/>
       <c r="E537" s="5"/>
@@ -23845,7 +23845,7 @@
     </row>
     <row r="538">
       <c r="A538" s="3"/>
-      <c r="B538" s="11"/>
+      <c r="B538" s="14"/>
       <c r="C538" s="5"/>
       <c r="D538" s="5"/>
       <c r="E538" s="5"/>
@@ -23861,7 +23861,7 @@
     </row>
     <row r="539">
       <c r="A539" s="3"/>
-      <c r="B539" s="11"/>
+      <c r="B539" s="14"/>
       <c r="C539" s="5"/>
       <c r="D539" s="5"/>
       <c r="E539" s="5"/>
@@ -23877,7 +23877,7 @@
     </row>
     <row r="540">
       <c r="A540" s="3"/>
-      <c r="B540" s="11"/>
+      <c r="B540" s="14"/>
       <c r="C540" s="5"/>
       <c r="D540" s="5"/>
       <c r="E540" s="5"/>
@@ -23893,7 +23893,7 @@
     </row>
     <row r="541">
       <c r="A541" s="3"/>
-      <c r="B541" s="11"/>
+      <c r="B541" s="14"/>
       <c r="C541" s="5"/>
       <c r="D541" s="5"/>
       <c r="E541" s="5"/>
@@ -23909,7 +23909,7 @@
     </row>
     <row r="542">
       <c r="A542" s="3"/>
-      <c r="B542" s="11"/>
+      <c r="B542" s="14"/>
       <c r="C542" s="5"/>
       <c r="D542" s="5"/>
       <c r="E542" s="5"/>
@@ -23925,7 +23925,7 @@
     </row>
     <row r="543">
       <c r="A543" s="3"/>
-      <c r="B543" s="11"/>
+      <c r="B543" s="14"/>
       <c r="C543" s="5"/>
       <c r="D543" s="5"/>
       <c r="E543" s="5"/>
@@ -23941,7 +23941,7 @@
     </row>
     <row r="544">
       <c r="A544" s="3"/>
-      <c r="B544" s="11"/>
+      <c r="B544" s="14"/>
       <c r="C544" s="5"/>
       <c r="D544" s="5"/>
       <c r="E544" s="5"/>
@@ -23957,7 +23957,7 @@
     </row>
     <row r="545">
       <c r="A545" s="3"/>
-      <c r="B545" s="11"/>
+      <c r="B545" s="14"/>
       <c r="C545" s="5"/>
       <c r="D545" s="5"/>
       <c r="E545" s="5"/>
@@ -23973,7 +23973,7 @@
     </row>
     <row r="546">
       <c r="A546" s="3"/>
-      <c r="B546" s="11"/>
+      <c r="B546" s="14"/>
       <c r="C546" s="5"/>
       <c r="D546" s="5"/>
       <c r="E546" s="5"/>
@@ -23989,7 +23989,7 @@
     </row>
     <row r="547">
       <c r="A547" s="3"/>
-      <c r="B547" s="11"/>
+      <c r="B547" s="14"/>
       <c r="C547" s="5"/>
       <c r="D547" s="5"/>
       <c r="E547" s="5"/>
@@ -24005,7 +24005,7 @@
     </row>
     <row r="548">
       <c r="A548" s="3"/>
-      <c r="B548" s="11"/>
+      <c r="B548" s="14"/>
       <c r="C548" s="5"/>
       <c r="D548" s="5"/>
       <c r="E548" s="5"/>
@@ -24021,7 +24021,7 @@
     </row>
     <row r="549">
       <c r="A549" s="3"/>
-      <c r="B549" s="11"/>
+      <c r="B549" s="14"/>
       <c r="C549" s="5"/>
       <c r="D549" s="5"/>
       <c r="E549" s="5"/>
@@ -24037,7 +24037,7 @@
     </row>
     <row r="550">
       <c r="A550" s="3"/>
-      <c r="B550" s="11"/>
+      <c r="B550" s="14"/>
       <c r="C550" s="5"/>
       <c r="D550" s="5"/>
       <c r="E550" s="5"/>
@@ -24053,7 +24053,7 @@
     </row>
     <row r="551">
       <c r="A551" s="3"/>
-      <c r="B551" s="11"/>
+      <c r="B551" s="14"/>
       <c r="C551" s="5"/>
       <c r="D551" s="5"/>
       <c r="E551" s="5"/>
@@ -24069,7 +24069,7 @@
     </row>
     <row r="552">
       <c r="A552" s="3"/>
-      <c r="B552" s="11"/>
+      <c r="B552" s="14"/>
       <c r="C552" s="5"/>
       <c r="D552" s="5"/>
       <c r="E552" s="5"/>
@@ -24085,7 +24085,7 @@
     </row>
     <row r="553">
       <c r="A553" s="3"/>
-      <c r="B553" s="11"/>
+      <c r="B553" s="14"/>
       <c r="C553" s="5"/>
       <c r="D553" s="5"/>
       <c r="E553" s="5"/>
@@ -24101,7 +24101,7 @@
     </row>
     <row r="554">
       <c r="A554" s="3"/>
-      <c r="B554" s="11"/>
+      <c r="B554" s="14"/>
       <c r="C554" s="5"/>
       <c r="D554" s="5"/>
       <c r="E554" s="5"/>
@@ -24117,7 +24117,7 @@
     </row>
     <row r="555">
       <c r="A555" s="3"/>
-      <c r="B555" s="11"/>
+      <c r="B555" s="14"/>
       <c r="C555" s="5"/>
       <c r="D555" s="5"/>
       <c r="E555" s="5"/>
@@ -24133,7 +24133,7 @@
     </row>
     <row r="556">
       <c r="A556" s="3"/>
-      <c r="B556" s="11"/>
+      <c r="B556" s="14"/>
       <c r="C556" s="5"/>
       <c r="D556" s="5"/>
       <c r="E556" s="5"/>
@@ -24149,7 +24149,7 @@
     </row>
     <row r="557">
       <c r="A557" s="3"/>
-      <c r="B557" s="11"/>
+      <c r="B557" s="14"/>
       <c r="C557" s="5"/>
       <c r="D557" s="5"/>
       <c r="E557" s="5"/>
@@ -24165,7 +24165,7 @@
     </row>
     <row r="558">
       <c r="A558" s="3"/>
-      <c r="B558" s="11"/>
+      <c r="B558" s="14"/>
       <c r="C558" s="5"/>
       <c r="D558" s="5"/>
       <c r="E558" s="5"/>
@@ -24181,7 +24181,7 @@
     </row>
     <row r="559">
       <c r="A559" s="3"/>
-      <c r="B559" s="11"/>
+      <c r="B559" s="14"/>
       <c r="C559" s="5"/>
       <c r="D559" s="5"/>
       <c r="E559" s="5"/>
